--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00883B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00883B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBA848A7-EA80-4ED0-9B8A-01D2D3232DB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60693229-B072-4CB7-BCE5-2258F2B6F7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{166A5DFB-8E46-4C3B-BCEF-47D718AB81E7}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{B5E6D661-E14F-4024-9294-A5F9D2897DC0}"/>
   </bookViews>
   <sheets>
     <sheet name="00883B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1636,24 +1636,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27CEE90F-5D08-4168-9E27-25870AAE5736}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5451E88B-2A2B-4436-A357-33E3DF023351}">
   <dimension ref="A1:R44"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1681,7 +1682,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1711,7 +1712,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1757,7 +1758,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1807,7 +1808,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1861,7 +1862,7 @@
         <v>4.57</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1887,7 +1888,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>26</v>
       </c>
@@ -1943,7 +1944,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>26</v>
       </c>
@@ -1999,7 +2000,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="49">
         <v>2025</v>
       </c>
@@ -2053,7 +2054,7 @@
         <v>5.25</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>26</v>
       </c>
@@ -2109,7 +2110,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>26</v>
       </c>
@@ -2165,7 +2166,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>26</v>
       </c>
@@ -2221,7 +2222,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
         <v>26</v>
       </c>
@@ -2277,7 +2278,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
         <v>26</v>
       </c>
@@ -2333,7 +2334,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>26</v>
       </c>
@@ -2389,7 +2390,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
         <v>26</v>
       </c>
@@ -2445,7 +2446,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
         <v>26</v>
       </c>
@@ -2501,7 +2502,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
         <v>26</v>
       </c>
@@ -2557,7 +2558,7 @@
         <v>0.48</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>26</v>
       </c>
@@ -2613,7 +2614,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>26</v>
       </c>
@@ -2669,7 +2670,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>26</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="51">
         <v>2024</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>26</v>
       </c>
@@ -2835,7 +2836,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>26</v>
       </c>
@@ -2891,7 +2892,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>26</v>
       </c>
@@ -2947,7 +2948,7 @@
         <v>0.43</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>26</v>
       </c>
@@ -3003,7 +3004,7 @@
         <v>0.44</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>26</v>
       </c>
@@ -3059,7 +3060,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -3115,7 +3116,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3171,7 +3172,7 @@
         <v>1.07</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="49">
         <v>2023</v>
       </c>
@@ -3225,7 +3226,7 @@
         <v>4.3600000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>26</v>
       </c>
@@ -3281,7 +3282,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>26</v>
       </c>
@@ -3337,7 +3338,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="19" t="s">
         <v>26</v>
       </c>
@@ -3393,7 +3394,7 @@
         <v>1.03</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
         <v>26</v>
       </c>
@@ -3449,7 +3450,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="51">
         <v>2022</v>
       </c>
@@ -3503,7 +3504,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>26</v>
       </c>
@@ -3559,7 +3560,7 @@
         <v>0.98</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>26</v>
       </c>
@@ -3615,7 +3616,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
         <v>26</v>
       </c>
@@ -3671,7 +3672,7 @@
         <v>0.91</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
         <v>26</v>
       </c>
@@ -3727,7 +3728,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="49">
         <v>2021</v>
       </c>
@@ -3781,7 +3782,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>26</v>
       </c>
@@ -3837,7 +3838,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3893,7 +3894,7 @@
         <v>0.71</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="19" t="s">
         <v>26</v>
       </c>
@@ -3949,7 +3950,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="51" t="s">
         <v>83</v>
       </c>
